--- a/timetable_input.xlsx
+++ b/timetable_input.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Network Theory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Discrete Mathematics</t>
+          <t>Signals and Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Digital Logic</t>
+          <t>Analog Circuits</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Object Oriented Prog.</t>
+          <t>Digital Design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Structures Tut</t>
+          <t>Network Theory Tutorial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Discrete Math Tut</t>
+          <t>Signals and Systems Tutorial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Digital Logic Tut</t>
+          <t>Analog Circuits Tutorial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Data Structures Lab</t>
+          <t>Analog Circuits Lab</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OOP Lab</t>
+          <t>Digital Design Lab</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Database Systems</t>
+          <t>Electromagnetics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Control Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Software Engineering</t>
+          <t>Power Systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1466,14 +1466,14 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Theory of Computation</t>
+          <t>Microprocessors</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1505,14 +1505,14 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Database Systems Lab</t>
+          <t>Control Systems Lab</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating Systems Lab</t>
+          <t>Communication Systems Lab</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Computer Networks Lab</t>
+          <t>Power Systems Lab</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Software Eng. Lab</t>
+          <t>Microprocessors Lab</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>E3 Elective 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>E3 Elective 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cryptography</t>
+          <t>E3 Elective 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Advanced Machine Learning</t>
+          <t>Advanced EEE Elective</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MTech Core Course 1</t>
+          <t>Linear Systems Theory</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1888,14 +1888,14 @@
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MTech Core Course 2</t>
+          <t>Optimal Control</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1927,14 +1927,14 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MTech Core Course 3</t>
+          <t>Advanced Digital Signal Processing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1966,14 +1966,14 @@
         <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MTech Core Course 4</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2005,14 +2005,14 @@
         <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MTech Core Course 5</t>
+          <t>Statistical Signal Processing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2044,14 +2044,14 @@
         <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MTech Core Course 6</t>
+          <t>Advanced Electromagnetic Engineering</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MTech Core Course 7</t>
+          <t>Microwave Circuits</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2122,14 +2122,14 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MTech Core Course 8</t>
+          <t>RF IC Design</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2161,14 +2161,14 @@
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTech Core Course 9</t>
+          <t>State Estimation and Filtering</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2200,14 +2200,14 @@
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MTech Core Course 10</t>
+          <t>Nonlinear Systems</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2239,14 +2239,14 @@
         <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MTech Core Course 11</t>
+          <t>Robotics and Automation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2278,14 +2278,14 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>H0</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MTech Core Course 12</t>
+          <t>Digital VLSI Design</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MTech Core Course 13</t>
+          <t>Analog VLSI Design</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MTech Core Course 14</t>
+          <t>VLSI CAD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MTech Core Course 15</t>
+          <t>Advanced Power Electronics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTech Core Course 16</t>
+          <t>Power System Dynamics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2495,12 +2495,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L501</t>
+          <t>L5001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MTech Lab 1</t>
+          <t>CE Lab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L502</t>
+          <t>L5002</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MTech Lab 2</t>
+          <t>MPRF Lab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L503</t>
+          <t>L5003</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MTech Lab 3</t>
+          <t>SCA Lab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2624,12 +2624,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L504</t>
+          <t>L5004</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MTech Lab 4</t>
+          <t>VLSI Lab</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L505</t>
+          <t>L5005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MTech Lab 5</t>
+          <t>PE Lab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2710,12 +2710,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L506</t>
+          <t>L5006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MTech Lab 6</t>
+          <t>CE Advanced Lab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L507</t>
+          <t>L5007</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MTech Lab 7</t>
+          <t>PE Advanced Lab</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elective Course 1</t>
+          <t>EE4032 - 5G Wireless Networks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Elective Course 2</t>
+          <t>EE4033 - Simulation Techniques for Communication Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Elective Course 3</t>
+          <t>EE5031 - Information Theory</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Elective Course 4</t>
+          <t>EE5042 - Optimization Techniques</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Elective Course 5</t>
+          <t>EE5134 - Electrical Power Quality and Reliability</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Elective Course 6</t>
+          <t>EE5235 - Optical Measurement Techniques and Applications</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Elective Course 7</t>
+          <t>EE5237 - Terahertz Electronics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Elective Course 8</t>
+          <t>EE5239 - RTL to GDSII</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Elective Course 9</t>
+          <t>EE5334 - Speech Signal Processing and Coding</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Elective Course 10</t>
+          <t>EE5336 - Pattern Recognition and Machine Learning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Elective Course 11</t>
+          <t>EE5340 - Video Analytics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Elective Course 12</t>
+          <t>EE5341 - Deep Learning for Vision, Language, Intelligent Systems</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Elective Course 13</t>
+          <t>EE5432 - Fundamentals of VLSI CAD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Elective Course 14</t>
+          <t>EE5434 - VLSI DSP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Elective Course 15</t>
+          <t>EE5440 - Spintronics and memory technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Elective Course 16</t>
+          <t>EE5447 - Epitaxy of Semiconductors</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Elective Course 17</t>
+          <t>EE5536 - Introduction to Distributed Control Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Elective Course 18</t>
+          <t>EE5538 - Advanced Control for Autonomous and Robotic Systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Elective Course 19</t>
+          <t>EE5540 - Graph Operators and Learning</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Open Elective 1</t>
+          <t>EE5042 - Optimization Techniques (Open Elective)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Open Elective 2</t>
+          <t>EE5540 - Graph Operators and Learning (Open Elective)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
